--- a/etf_holdings/2026-10-27_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-27_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,16 +451,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,24 +469,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00981A(1,073,000)、00991A(300,000)、00403A(399,000)</t>
+          <t>00981A(80,000)、00403A(55,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00400A(全數賣出)</t>
+          <t>00405A(-150,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -499,54 +499,54 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00981A(80,000)、00403A(55,000)</t>
+          <t>00981A(1,073,000)、00991A(300,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00405A(-150,000)</t>
+          <t>00403A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00991A(200,000)、00407A(400,000)</t>
+          <t>00981A(50,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00403A(全數賣出)、00405A(-70,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -554,29 +554,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>00991A(200,000)、00407A(400,000)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>00403A(-4,000,000)、00400A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,24 +589,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00981A(969,000)</t>
+          <t>00981A(80,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00400A(全數賣出)</t>
+          <t>00403A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -619,132 +619,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00407A(40,000)</t>
+          <t>00981A(969,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00400A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>00407A(50,000)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>00400A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00403A(14,000)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>00400A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>00407A(-80,000)、00400A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>00981A(50,000)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00405A(-70,000)</t>
+          <t>00403A(全數賣出)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-10-27_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-27_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00981A(80,000)、00403A(55,000)</t>
+          <t>00403A(55,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -490,141 +490,21 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00981A(1,073,000)、00991A(300,000)</t>
+          <t>00991A(300,000)、00403A(399,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00403A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>00981A(50,000)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00403A(全數賣出)、00405A(-70,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00991A(200,000)、00407A(400,000)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>00981A(80,000)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>00403A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>00981A(969,000)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>00403A(全數賣出)</t>
         </is>
       </c>
     </row>
